--- a/juridique/registre-traitements-rgpd.xlsx
+++ b/juridique/registre-traitements-rgpd.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>

--- a/juridique/registre-traitements-rgpd.xlsx
+++ b/juridique/registre-traitements-rgpd.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Formspree (réception du formulaire) ; service de messagerie ; outil de visioconférence.</t>
+          <t>Hébergeur du site ; Formspree (réception du formulaire, si activé) ; service de messagerie ; outil de visioconférence.</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1422,25 +1422,52 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>Hébergeur du site</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Hébergement et diffusion du site internet</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>{{HEBERGEUR_NOM}}</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>{{HEBERGEUR_LOCALISATION}}</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Conditions du fournisseur (art. 28) ; clauses contractuelles types ; aucune donnée de dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>Formspree</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Formulaire de contact</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>{{FORMSPREE_ENTITE}}</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>{{FORMSPREE_HEBERGEMENT}}</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Clauses contractuelles types (États-Unis)</t>
         </is>

--- a/juridique/registre-traitements-rgpd.xlsx
+++ b/juridique/registre-traitements-rgpd.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
